--- a/CRONOGRAMA - ASSUNTO.xlsx
+++ b/CRONOGRAMA - ASSUNTO.xlsx
@@ -26,8 +26,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -150,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -204,7 +204,8 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -918,8 +919,8 @@
           <t>Início do plano</t>
         </is>
       </c>
-      <c r="B2" s="21" t="n">
-        <v>46315</v>
+      <c r="B2" s="22" t="n">
+        <v>46321</v>
       </c>
     </row>
     <row r="4"/>

--- a/CRONOGRAMA - ASSUNTO.xlsx
+++ b/CRONOGRAMA - ASSUNTO.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Legislação_e_História_PE" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Matérias_Específicas_Outras" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Config_App" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Registro_Estudos" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -929,6 +930,71 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Matéria</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cód</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dir. Constitucional &amp; DH</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>DIR-CONST-01</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Pomodoro</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4340,7 +4406,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>Não Iniciado</t>
+          <t>Em Andamento</t>
         </is>
       </c>
       <c r="N5" s="7" t="n"/>

--- a/CRONOGRAMA - ASSUNTO.xlsx
+++ b/CRONOGRAMA - ASSUNTO.xlsx
@@ -25,10 +25,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -4406,7 +4405,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>Em Andamento</t>
+          <t>Não Iniciado</t>
         </is>
       </c>
       <c r="N5" s="7" t="n"/>

--- a/CRONOGRAMA - ASSUNTO.xlsx
+++ b/CRONOGRAMA - ASSUNTO.xlsx
@@ -25,9 +25,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -150,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -206,6 +207,9 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -677,7 +681,7 @@
         <v/>
       </c>
       <c r="H5" s="20" t="n">
-        <v>0</v>
+        <v>0.01492537313432836</v>
       </c>
     </row>
     <row r="6">
@@ -716,7 +720,7 @@
         <v/>
       </c>
       <c r="H6" s="20" t="n">
-        <v>0</v>
+        <v>0.009523809523809525</v>
       </c>
     </row>
     <row r="7">
@@ -755,7 +759,7 @@
         <v/>
       </c>
       <c r="H7" s="20" t="n">
-        <v>0</v>
+        <v>0.009615384615384616</v>
       </c>
     </row>
     <row r="8">
@@ -794,7 +798,7 @@
         <v/>
       </c>
       <c r="H8" s="20" t="n">
-        <v>0</v>
+        <v>0.009174311926605505</v>
       </c>
     </row>
     <row r="9"/>
@@ -4376,7 +4380,9 @@
         </is>
       </c>
       <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
+      <c r="F5" s="23" t="n">
+        <v>46319</v>
+      </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
@@ -4405,7 +4411,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t>Não Iniciado</t>
+          <t>Concluído</t>
         </is>
       </c>
       <c r="N5" s="7" t="n"/>

--- a/CRONOGRAMA - ASSUNTO.xlsx
+++ b/CRONOGRAMA - ASSUNTO.xlsx
@@ -992,6 +992,29 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="22" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dir. Constitucional &amp; DH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>DIR-CONST-01</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>60</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+    </row>
     <row r="4"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CRONOGRAMA - ASSUNTO.xlsx
+++ b/CRONOGRAMA - ASSUNTO.xlsx
@@ -1015,7 +1015,29 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="A4" s="22" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dir. Constitucional &amp; DH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>DIR-CONST-01</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>60</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CRONOGRAMA - ASSUNTO.xlsx
+++ b/CRONOGRAMA - ASSUNTO.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Matérias_Específicas_Outras" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Config_App" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Registro_Estudos" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Plano_Diario" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1043,6 +1044,51 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Item do plano</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Feito</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bloco 1 (1h30): Revisão Semanal Consolidada</t>
+        </is>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4"/>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/CRONOGRAMA - ASSUNTO.xlsx
+++ b/CRONOGRAMA - ASSUNTO.xlsx
@@ -1083,6 +1083,19 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="22" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bloco 2 (1h30): Organização da Próxima Semana</t>
+        </is>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+    </row>
     <row r="4"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/CRONOGRAMA - ASSUNTO.xlsx
+++ b/CRONOGRAMA - ASSUNTO.xlsx
@@ -1096,7 +1096,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4"/>
+    <row r="4">
+      <c r="A4" s="22" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Revisão do Dia (30min): Planejamento Semanal</t>
+        </is>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/CRONOGRAMA - ASSUNTO.xlsx
+++ b/CRONOGRAMA - ASSUNTO.xlsx
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1106,6 +1106,19 @@
         </is>
       </c>
       <c r="C4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Meta de Questões: 20 questões</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
         <v>1</v>
       </c>
     </row>

--- a/CRONOGRAMA - ASSUNTO.xlsx
+++ b/CRONOGRAMA - ASSUNTO.xlsx
@@ -1050,7 +1050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,6 +1119,19 @@
         </is>
       </c>
       <c r="C5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bloco 3 (1h - Exercícios): Descanso / Lazer Ativo</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
         <v>1</v>
       </c>
     </row>

--- a/CRONOGRAMA - ASSUNTO.xlsx
+++ b/CRONOGRAMA - ASSUNTO.xlsx
@@ -26,10 +26,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -4527,7 +4526,7 @@
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Pendente</t>
+          <t>Feito</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
